--- a/artfynd/A 11843-2023 artfynd.xlsx
+++ b/artfynd/A 11843-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121521397</v>
       </c>
       <c r="B2" t="n">
-        <v>57370</v>
+        <v>57371</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>121521396</v>
       </c>
       <c r="B3" t="n">
-        <v>97052</v>
+        <v>97058</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 11843-2023 artfynd.xlsx
+++ b/artfynd/A 11843-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121521397</v>
       </c>
       <c r="B2" t="n">
-        <v>57371</v>
+        <v>57372</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>121521396</v>
       </c>
       <c r="B3" t="n">
-        <v>97058</v>
+        <v>97059</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 11843-2023 artfynd.xlsx
+++ b/artfynd/A 11843-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121521397</v>
+        <v>121521396</v>
       </c>
       <c r="B2" t="n">
-        <v>57372</v>
+        <v>97059</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563312</v>
+        <v>563309</v>
       </c>
       <c r="R2" t="n">
-        <v>6999985</v>
+        <v>6999970</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Högstubbe</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121521396</v>
+        <v>121521397</v>
       </c>
       <c r="B3" t="n">
-        <v>97059</v>
+        <v>57372</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,38 +789,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563309</v>
+        <v>563312</v>
       </c>
       <c r="R3" t="n">
-        <v>6999970</v>
+        <v>6999985</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,6 +857,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Högstubbe</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 11843-2023 artfynd.xlsx
+++ b/artfynd/A 11843-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121521396</v>
+        <v>121521397</v>
       </c>
       <c r="B2" t="n">
-        <v>97059</v>
+        <v>57373</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563309</v>
+        <v>563312</v>
       </c>
       <c r="R2" t="n">
-        <v>6999970</v>
+        <v>6999985</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +755,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Högstubbe</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121521397</v>
+        <v>121521396</v>
       </c>
       <c r="B3" t="n">
-        <v>57372</v>
+        <v>97067</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,42 +798,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563312</v>
+        <v>563309</v>
       </c>
       <c r="R3" t="n">
-        <v>6999985</v>
+        <v>6999970</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,11 +862,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Högstubbe</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 11843-2023 artfynd.xlsx
+++ b/artfynd/A 11843-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121521396</v>
+        <v>121521397</v>
       </c>
       <c r="B2" t="n">
-        <v>97067</v>
+        <v>57373</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563309</v>
+        <v>563312</v>
       </c>
       <c r="R2" t="n">
-        <v>6999970</v>
+        <v>6999985</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +755,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Högstubbe</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121521397</v>
+        <v>121521396</v>
       </c>
       <c r="B3" t="n">
-        <v>57373</v>
+        <v>97067</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,42 +798,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563312</v>
+        <v>563309</v>
       </c>
       <c r="R3" t="n">
-        <v>6999985</v>
+        <v>6999970</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,11 +862,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Högstubbe</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 11843-2023 artfynd.xlsx
+++ b/artfynd/A 11843-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121521397</v>
+        <v>121521396</v>
       </c>
       <c r="B2" t="n">
-        <v>57373</v>
+        <v>97067</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563312</v>
+        <v>563309</v>
       </c>
       <c r="R2" t="n">
-        <v>6999985</v>
+        <v>6999970</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Högstubbe</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121521396</v>
+        <v>121521397</v>
       </c>
       <c r="B3" t="n">
-        <v>97067</v>
+        <v>57373</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,38 +789,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563309</v>
+        <v>563312</v>
       </c>
       <c r="R3" t="n">
-        <v>6999970</v>
+        <v>6999985</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,6 +857,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Högstubbe</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 11843-2023 artfynd.xlsx
+++ b/artfynd/A 11843-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>121521397</v>
       </c>
       <c r="B2" t="n">
-        <v>57373</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -786,50 +781,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121521396</v>
+        <v>121521398</v>
       </c>
       <c r="B3" t="n">
-        <v>97067</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58388</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>103001</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563309</v>
+        <v>563316</v>
       </c>
       <c r="R3" t="n">
-        <v>6999970</v>
+        <v>6999975</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,6 +879,103 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121521396</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Stadsforsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>563309</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6999970</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11843-2023 artfynd.xlsx
+++ b/artfynd/A 11843-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121521397</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121521398</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -976,8 +991,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121521396</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>